--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260918.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260918.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>4.04%</t>
+          <t>3.99%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.93%</t>
+          <t>3.94%</t>
         </is>
       </c>
     </row>
@@ -682,51 +682,51 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.02%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>台灣大哥</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>37,372,000</t>
+          <t>51,253,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.00%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>台灣大哥</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>51,253,000</t>
+          <t>37,372,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>2.99%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>2.97%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>2.80%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>4,283,475,863</t>
+          <t>4,299,222,641</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>2.77%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.71%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>2.63%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
@@ -880,24 +880,24 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>6,990,000</t>
+          <t>33,103,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,110 +909,110 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>33,103,000</t>
+          <t>6,990,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>4,101,000</t>
+          <t>585,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>10,091,000</t>
+          <t>4,101,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.40%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>23,080,000</t>
+          <t>10,091,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>585,000</t>
+          <t>23,080,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.31%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.24%</t>
         </is>
       </c>
     </row>
@@ -1056,29 +1056,29 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.20%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>信邦電子</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>9,893,000</t>
+          <t>2,939,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.13%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
@@ -1122,29 +1122,29 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>信邦電子</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>2,939,000</t>
+          <t>9,893,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
@@ -1188,95 +1188,95 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.89%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>5,434,000</t>
+          <t>14,684,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>14,684,000</t>
+          <t>5,434,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.82%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,643,121,204</t>
+          <t>17,775,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>17,775,000</t>
+          <t>2,749,711,204</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.77%</t>
         </is>
       </c>
     </row>
@@ -1298,46 +1298,46 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.68%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>鴻海精密</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>10,015,000</t>
+          <t>9,344,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.62%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>矽格股份</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>6,795,000</t>
+          <t>10,287,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,66 +1349,66 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>鴻海精密</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>6,478,000</t>
+          <t>10,015,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.62%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>矽格股份</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>10,287,000</t>
+          <t>6,795,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.61%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>9,344,000</t>
+          <t>6,478,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
@@ -1430,46 +1430,46 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>至上電子</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>26,620,004</t>
+          <t>3,901,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>元太科技</t>
+          <t>至上電子</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>14,913,000</t>
+          <t>26,620,004</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,22 +1481,22 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>元太科技</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>3,901,000</t>
+          <t>14,913,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>50,331,000</t>
+          <t>9,000,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>9,000,000</t>
+          <t>50,331,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -1672,24 +1672,24 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>瀚宇博德</t>
+          <t>致伸科技</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>17,681,000</t>
+          <t>20,037,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,22 +1701,22 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>致伸科技</t>
+          <t>瀚宇博德</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>20,037,000</t>
+          <t>17,681,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-18,901,008</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
